--- a/data/BASES/TAREAS.xlsx
+++ b/data/BASES/TAREAS.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="36">
   <si>
     <t>SIGUIENTE FOLIO</t>
   </si>
@@ -119,6 +119,18 @@
   </si>
   <si>
     <t>SE DESCOPUSO POR UN DERRAME ACCIDENTAL DE LIQUIDO</t>
+  </si>
+  <si>
+    <t>REPARAR EQUIPO RH PRUEBA</t>
+  </si>
+  <si>
+    <t>NO PRENDE EL EQUIPO PRUEBA FINAL</t>
+  </si>
+  <si>
+    <t>C:\OCXRST\OrdendeComprasRST\data\BASES\ADJUNTOS_TAREAS\T-0002\1c5cbb17-a41b-4560-9bbb-4ceb3caa2272_TAREAS_EXPORTADAS.xlsx</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
   </si>
 </sst>
 </file>
@@ -559,13 +571,13 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>24</v>
@@ -615,7 +627,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -634,7 +646,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1">
@@ -645,6 +657,14 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BASES/TAREAS.xlsx
+++ b/data/BASES/TAREAS.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="37">
   <si>
     <t>SIGUIENTE FOLIO</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>Pendiente</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
   </si>
 </sst>
 </file>
@@ -589,7 +592,7 @@
         <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
         <v>28</v>
